--- a/Design_Docs/Instruction_Word_Table.xlsx
+++ b/Design_Docs/Instruction_Word_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\Design_Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431176F9-152D-4D0B-BDE9-B20732E49C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B0F89D-BBC6-4154-B4F3-507F1FC61033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="141">
   <si>
     <t>Instruction</t>
   </si>
@@ -446,13 +446,22 @@
     <t>imm[12] imm[10:5] rs2 rs1 funct3 imm[4:1] imm[11] opcode</t>
   </si>
   <si>
-    <t>imm[20] imm[10:1] imm[11] imm[19:12] rd opcode</t>
-  </si>
-  <si>
     <t>Func7/Imm0</t>
   </si>
   <si>
     <t>0100011</t>
+  </si>
+  <si>
+    <t>Imm[20]</t>
+  </si>
+  <si>
+    <t>Imm[10:1]</t>
+  </si>
+  <si>
+    <t>Imm[11]</t>
+  </si>
+  <si>
+    <t>Imm[19:12]</t>
   </si>
 </sst>
 </file>
@@ -878,17 +887,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC39E31-91A3-430A-827B-8D1C1B6215BF}">
   <dimension ref="A2:K54"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.453125" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" customWidth="1"/>
-    <col min="5" max="5" width="18.7265625" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" customWidth="1"/>
-    <col min="9" max="9" width="37.1796875" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" customWidth="1"/>
+    <col min="9" max="9" width="42.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
@@ -1221,7 +1230,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>71</v>
@@ -1590,7 +1599,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="28.25" customHeight="1">
+    <row r="27" spans="1:9" ht="28.2" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -1619,7 +1628,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="28.25" customHeight="1">
+    <row r="28" spans="1:9" ht="28.2" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -1648,7 +1657,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="28.25" customHeight="1">
+    <row r="29" spans="1:9" ht="28.2" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>41</v>
       </c>
@@ -1827,7 +1836,7 @@
         <v>118</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>115</v>
@@ -1856,7 +1865,7 @@
         <v>118</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>114</v>
@@ -1885,7 +1894,7 @@
         <v>118</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>116</v>
@@ -2233,16 +2242,16 @@
         <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>7</v>
@@ -2255,9 +2264,7 @@
       </c>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="10" t="s">
-        <v>135</v>
-      </c>
+      <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
